--- a/Digital-Business-Toolkit/05-CashFlow/Product.xlsx
+++ b/Digital-Business-Toolkit/05-CashFlow/Product.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Main Workspace" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Quick Start" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="User Guide" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="לוח בקרה" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="שולחן עבודה" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="התחלה מהירה" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="מדריך שימוש" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -365,7 +365,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Main Workspace'!H3</f>
+              <f>'שולחן עבודה'!H3</f>
             </strRef>
           </tx>
           <spPr>
@@ -383,12 +383,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Main Workspace'!$A$4:$A$15</f>
+              <f>'שולחן עבודה'!$A$4:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Main Workspace'!$H$4:$H$15</f>
+              <f>'שולחן עבודה'!$H$4:$H$15</f>
             </numRef>
           </val>
         </ser>
@@ -788,7 +788,7 @@
     <row r="2" ht="46" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Cash Flow Planner — Dashboard</t>
+          <t>לוח בקרה — תכנון תזרים מזומנים</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -799,7 +799,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ContractorOS — Know your cash runway before it's a problem</t>
+          <t>ContractorOS — דעו כמה זמן המזומן שלכם יחזיק, לפני שזו בעיה</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -830,48 +830,48 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Cash Runway (חודשים)</t>
+          <t>טווח החזקת מזומן (חודשים)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="B6" s="6">
-        <f>'Main Workspace'!H15</f>
+        <f>'שולחן עבודה'!H15</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>AVERAGE('Main Workspace'!G4:G15)</f>
+        <f>AVERAGE('שולחן עבודה'!G4:G15)</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>COUNTIF('Main Workspace'!G4:G15,"&lt;0")</f>
+        <f>COUNTIF('שולחן עבודה'!G4:G15,"&lt;0")</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>MIN('Main Workspace'!H4:H15)</f>
+        <f>MIN('שולחן עבודה'!H4:H15)</f>
         <v/>
       </c>
       <c r="F6" s="7">
-        <f>IF(AVERAGE('Main Workspace'!G4:G15)&gt;=0,"∞",'Main Workspace'!H15/-AVERAGE('Main Workspace'!G4:G15))</f>
+        <f>IF(AVERAGE('שולחן עבודה'!G4:G15)&gt;=0,"∞",'שולחן עבודה'!H15/-AVERAGE('שולחן עבודה'!G4:G15))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>⚠ Business Insights / התראות</t>
+          <t>⚠ תובנות עסקיות והתראות</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="B10" s="9">
-        <f>IF(COUNTIF('Main Workspace'!G4:G15,"&lt;0")&gt;0,"יש "&amp;COUNTIF('Main Workspace'!G4:G15,"&lt;0")&amp;" חודשים עם נטו שלילי — בדקו תזמון הוצאות.","כל החודשים ברווח נטו חיובי.")</f>
+        <f>IF(COUNTIF('שולחן עבודה'!G4:G15,"&lt;0")&gt;0,"יש "&amp;COUNTIF('שולחן עבודה'!G4:G15,"&lt;0")&amp;" חודשים עם נטו שלילי — בדקו תזמון הוצאות.","כל החודשים ברווח נטו חיובי.")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="B11" s="10">
-        <f>IF(MIN('Main Workspace'!H4:H15)&lt;0,"יש חודש עם יתרת סגירה שלילית — סיכון ממשי לתזרים!","היתרה החודשית נשארת חיובית לאורך כל השנה.")</f>
+        <f>IF(MIN('שולחן עבודה'!H4:H15)&lt;0,"יש חודש עם יתרת סגירה שלילית — סיכון ממשי לתזרים!","היתרה החודשית נשארת חיובית לאורך כל השנה.")</f>
         <v/>
       </c>
     </row>
@@ -910,7 +910,7 @@
     <row r="1" ht="44" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>תכנון תזרים מזומנים | Cash Flow Planner</t>
+          <t>תכנון תזרים מזומנים</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1386,7 +1386,7 @@
     <row r="1" ht="44" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>התחלה מהירה | Quick Start</t>
+          <t>התחלה מהירה</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1402,7 +1402,7 @@
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t>1. עברו ללשונית 'Main Workspace' — טבלת 12 החודשים כבר מוכנה.</t>
+          <t>1. עברו ללשונית 'שולחן עבודה' — טבלת 12 החודשים כבר מוכנה.</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>5. עברו ל-Dashboard לראות את יתרת הסגירה, החודשים החלשים, ואת ה-Cash Runway.</t>
+          <t>5. עברו ל-לוח הבקרה לראות את יתרת הסגירה, החודשים החלשים, ואת טווח החזקת המזומן.</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
     <row r="1" ht="44" customHeight="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>מדריך שימוש | User Guide</t>
+          <t>מדריך שימוש</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1564,19 +1564,19 @@
     <row r="10" ht="46" customHeight="1">
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>מה Dashboard מציג?</t>
+          <t>מה לוח הבקרה מציג?</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>יתרת סגירה נוכחית, ממוצע נטו חודשי, מספר חודשים בגירעון, היתרה הנמוכה ביותר, ו-Cash Runway.</t>
+          <t>יתרת סגירה נוכחית, ממוצע נטו חודשי, מספר חודשים בגירעון, היתרה הנמוכה ביותר, וטווח החזקת המזומן.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>מה זה Cash Runway?</t>
+          <t>מה זה טווח החזקת מזומן?</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -1600,7 +1600,7 @@
     <row r="14">
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>שאלות נפוצות (FAQ)</t>
+          <t>שאלות נפוצות</t>
         </is>
       </c>
     </row>

--- a/Digital-Business-Toolkit/05-CashFlow/Product.xlsx
+++ b/Digital-Business-Toolkit/05-CashFlow/Product.xlsx
@@ -799,7 +799,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ContractorOS — דעו כמה זמן המזומן שלכם יחזיק, לפני שזו בעיה</t>
+          <t>JobMargin — דעו כמה זמן המזומן שלכם יחזיק, לפני שזו בעיה</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
